--- a/resources/qa_test/formula_samples/_test_formula_sum.xlsx
+++ b/resources/qa_test/formula_samples/_test_formula_sum.xlsx
@@ -486,27 +486,27 @@
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>999</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>999</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2" t="n">
         <f aca="false">SUM(B3:E3)</f>
-        <v>2046</v>
+        <v>1045</v>
       </c>
       <c r="G3" s="2" t="n">
         <f aca="false">AVERAGE(B3:E3)</f>
-        <v>511.5</v>
+        <v>261.25</v>
       </c>
       <c r="H3" s="2" t="n">
         <f aca="false">MAX(B3:E3)</f>
@@ -515,242 +515,282 @@
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="F4" s="2" t="n">
         <f aca="false">SUM(B4:E4)</f>
-        <v>205</v>
+        <v>96</v>
       </c>
       <c r="G4" s="2" t="n">
         <f aca="false">AVERAGE(B4:E4)</f>
-        <v>51.25</v>
+        <v>24</v>
       </c>
       <c r="H4" s="2" t="n">
         <f aca="false">MAX(B4:E4)</f>
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="n">
         <f aca="false">SUM(B5:E5)</f>
-        <v>296</v>
+        <v>136</v>
       </c>
       <c r="G5" s="2" t="n">
         <f aca="false">AVERAGE(B5:E5)</f>
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="H5" s="2" t="n">
         <f aca="false">MAX(B5:E5)</f>
-        <v>78</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="F6" s="2" t="n">
         <f aca="false">SUM(B6:E6)</f>
-        <v>336</v>
+        <v>176</v>
       </c>
       <c r="G6" s="2" t="n">
         <f aca="false">AVERAGE(B6:E6)</f>
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="H6" s="2" t="n">
         <f aca="false">MAX(B6:E6)</f>
-        <v>88</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="F7" s="2" t="n">
         <f aca="false">SUM(B7:E7)</f>
-        <v>376</v>
+        <v>296</v>
       </c>
       <c r="G7" s="2" t="n">
         <f aca="false">AVERAGE(B7:E7)</f>
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="H7" s="2" t="n">
         <f aca="false">MAX(B7:E7)</f>
-        <v>98</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="F8" s="2" t="n">
         <f aca="false">SUM(B8:E8)</f>
-        <v>416</v>
+        <v>336</v>
       </c>
       <c r="G8" s="2" t="n">
         <f aca="false">AVERAGE(B8:E8)</f>
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="H8" s="2" t="n">
         <f aca="false">MAX(B8:E8)</f>
-        <v>108</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="F9" s="2" t="n">
         <f aca="false">SUM(B9:E9)</f>
-        <v>456</v>
+        <v>376</v>
       </c>
       <c r="G9" s="2" t="n">
         <f aca="false">AVERAGE(B9:E9)</f>
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2" t="n">
         <f aca="false">MAX(B9:E9)</f>
-        <v>118</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="F10" s="2" t="n">
         <f aca="false">SUM(B10:E10)</f>
-        <v>496</v>
+        <v>416</v>
       </c>
       <c r="G10" s="2" t="n">
         <f aca="false">AVERAGE(B10:E10)</f>
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="H10" s="2" t="n">
         <f aca="false">MAX(B10:E10)</f>
-        <v>128</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="n">
-        <v>99</v>
+        <v>11</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>118</v>
       </c>
       <c r="F11" s="2" t="n">
-        <f aca="false">SUM(F3:F10)</f>
-        <v>4627</v>
+        <f aca="false">SUM(B11:E11)</f>
+        <v>456</v>
       </c>
       <c r="G11" s="2" t="n">
-        <f aca="false">AVERAGE(F3:F10)</f>
-        <v>578.375</v>
+        <f aca="false">AVERAGE(B11:E11)</f>
+        <v>114</v>
       </c>
       <c r="H11" s="2" t="n">
-        <f aca="false">MAX(F3:F10)</f>
-        <v>2046</v>
+        <f aca="false">MAX(B11:E11)</f>
+        <v>118</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+        <v>12</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <f aca="false">SUM(B12:E12)</f>
+        <v>496</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <f aca="false">AVERAGE(B12:E12)</f>
+        <v>124</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <f aca="false">MAX(B12:E12)</f>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <f aca="false">SUM(F3:F12)</f>
+        <v>3829</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <f aca="false">AVERAGE(F3:F12)</f>
+        <v>382.9</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <f aca="false">MAX(F3:F12)</f>
+        <v>1045</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/resources/qa_test/formula_samples/_test_formula_sum.xlsx
+++ b/resources/qa_test/formula_samples/_test_formula_sum.xlsx
@@ -84,22 +84,25 @@
       <color theme="1"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
-      <charset val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -234,71 +237,11 @@
         <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
